--- a/exports/6876_toldopampa.xlsx
+++ b/exports/6876_toldopampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M217"/>
+  <dimension ref="A1:M218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12956,22 +12956,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>74951390</t>
+          <t>61744559</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>USCAMAYTA</t>
+          <t>TERREROS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>MEDALY MIRELLA</t>
+          <t>LESLY HEVILYN</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>23/02/2002</t>
+          <t>21/11/2002</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13019,22 +13019,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>21011813</t>
+          <t>74951390</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>USCAMAYTA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ESPERANZA</t>
+          <t>MEDALY MIRELLA</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13043,21 +13043,21 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>08/01/1968</t>
+          <t>23/02/2002</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>05/12/2012</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13082,45 +13082,45 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>60657088</t>
+          <t>21011813</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>BRAYAN RIKI</t>
+          <t>ESPERANZA</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>04/12/2001</t>
+          <t>08/01/1968</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>05/12/2012</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13145,22 +13145,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>21011828</t>
+          <t>60657088</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ENOCH ESEQUIEL</t>
+          <t>BRAYAN RIKI</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13169,21 +13169,21 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>04/06/1971</t>
+          <t>04/12/2001</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>26/09/2012</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13208,7 +13208,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>80038185</t>
+          <t>21011828</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>WILSON</t>
+          <t>ENOCH ESEQUIEL</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13232,11 +13232,11 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>03/10/1977</t>
+          <t>04/06/1971</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>27/06/2021</t>
+          <t>26/09/2012</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>48279651</t>
+          <t>80038185</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13281,25 +13281,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NELVA</t>
+          <t>WILSON</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>23/05/1994</t>
+          <t>03/10/1977</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>26/09/2012</t>
+          <t>27/06/2021</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>75847039</t>
+          <t>48279651</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>SADITH</t>
+          <t>NELVA</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13358,16 +13358,16 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>01/01/2001</t>
+          <t>23/05/1994</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>27/01/2012</t>
+          <t>26/09/2012</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13397,7 +13397,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>81359236</t>
+          <t>75847039</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13407,30 +13407,30 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>CALEB JAMES</t>
+          <t>SADITH</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>21/02/2016</t>
+          <t>01/01/2001</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>24/08/2016</t>
+          <t>27/01/2012</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13460,7 +13460,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>19870451</t>
+          <t>81359236</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13470,35 +13470,35 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ROSA MARINA</t>
+          <t>CALEB JAMES</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>27/06/1969</t>
+          <t>21/02/2016</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>24/08/2016</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13523,35 +13523,35 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>42350389</t>
+          <t>19870451</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LUIS CUVIAR</t>
+          <t>ROSA MARINA</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>06/04/1983</t>
+          <t>27/06/1969</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>29/11/2012</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13586,7 +13586,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>60501512</t>
+          <t>42350389</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13596,12 +13596,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>KENYI ANDY</t>
+          <t>LUIS CUVIAR</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>27/09/2005</t>
+          <t>06/04/1983</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>29/11/2012</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13649,7 +13649,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>62232531</t>
+          <t>60501512</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13664,20 +13664,20 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>SARELY</t>
+          <t>KENYI ANDY</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>19/11/2008</t>
+          <t>27/09/2005</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13712,7 +13712,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>19967640</t>
+          <t>62232531</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13722,35 +13722,35 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DIONISIO HUGO</t>
+          <t>SARELY</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>17/11/1959</t>
+          <t>19/11/2008</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13775,7 +13775,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>20406209</t>
+          <t>19967640</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>SILVINO AURELIO</t>
+          <t>DIONISIO HUGO</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13799,21 +13799,21 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>15/10/1968</t>
+          <t>17/11/1959</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>15/11/2019</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13838,7 +13838,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>91589995</t>
+          <t>20406209</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13848,30 +13848,30 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SOTELO</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>EYMI ETHEL</t>
+          <t>SILVINO AURELIO</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>13/11/2019</t>
+          <t>15/10/1968</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>13/11/2024</t>
+          <t>15/11/2019</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13901,22 +13901,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>20410598</t>
+          <t>91589995</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>SOTELO</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>JUANA ESPERANZA</t>
+          <t>EYMI ETHEL</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13925,16 +13925,16 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>30/12/1954</t>
+          <t>13/11/2019</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>29/08/2014</t>
+          <t>13/11/2024</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13964,7 +13964,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>19846445</t>
+          <t>20410598</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LUCILA</t>
+          <t>JUANA ESPERANZA</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13988,11 +13988,11 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>12/12/1958</t>
+          <t>30/12/1954</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>29/08/2014</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14027,63 +14027,126 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
+          <t>19846445</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>YUPANQUI</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LUCILA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>68</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>12/12/1958</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>5.ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>06/04/2015</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M217" t="n">
+        <v>120605</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
           <t>44438775</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>YUPANQUI</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>PARIACHI</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>EUDOVIA FLORINDA</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F217" t="n">
+      <c r="F218" t="n">
         <v>50</v>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>15/10/1976</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H218" t="inlineStr">
         <is>
           <t>4.ADULTO</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I218" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
         <is>
           <t>11/11/2013</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>PAMPA HERMOSA</t>
-        </is>
-      </c>
-      <c r="M217" t="n">
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M218" t="n">
         <v>120605</v>
       </c>
     </row>

--- a/exports/6876_toldopampa.xlsx
+++ b/exports/6876_toldopampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M218"/>
+  <dimension ref="A1:M217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12956,22 +12956,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>61744559</t>
+          <t>74951390</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TERREROS</t>
+          <t>USCAMAYTA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LESLY HEVILYN</t>
+          <t>MEDALY MIRELLA</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>21/11/2002</t>
+          <t>23/02/2002</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13019,22 +13019,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>74951390</t>
+          <t>21011813</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>USCAMAYTA</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>MEDALY MIRELLA</t>
+          <t>ESPERANZA</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13043,21 +13043,21 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>23/02/2002</t>
+          <t>08/01/1968</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>05/12/2012</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13082,45 +13082,45 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>21011813</t>
+          <t>60657088</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ESPERANZA</t>
+          <t>BRAYAN RIKI</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>08/01/1968</t>
+          <t>04/12/2001</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>05/12/2012</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13145,22 +13145,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>60657088</t>
+          <t>21011828</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>BRAYAN RIKI</t>
+          <t>ENOCH ESEQUIEL</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13169,21 +13169,21 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>04/12/2001</t>
+          <t>04/06/1971</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>26/09/2012</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13208,7 +13208,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>21011828</t>
+          <t>80038185</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ENOCH ESEQUIEL</t>
+          <t>WILSON</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13232,11 +13232,11 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>04/06/1971</t>
+          <t>03/10/1977</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>26/09/2012</t>
+          <t>27/06/2021</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>80038185</t>
+          <t>48279651</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13281,25 +13281,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>WILSON</t>
+          <t>NELVA</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>03/10/1977</t>
+          <t>23/05/1994</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>27/06/2021</t>
+          <t>26/09/2012</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>48279651</t>
+          <t>75847039</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NELVA</t>
+          <t>SADITH</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13358,16 +13358,16 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>23/05/1994</t>
+          <t>01/01/2001</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>26/09/2012</t>
+          <t>27/01/2012</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13397,7 +13397,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>75847039</t>
+          <t>81359236</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13407,30 +13407,30 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>SADITH</t>
+          <t>CALEB JAMES</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>01/01/2001</t>
+          <t>21/02/2016</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>27/01/2012</t>
+          <t>24/08/2016</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13460,7 +13460,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>81359236</t>
+          <t>19870451</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13470,35 +13470,35 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>CALEB JAMES</t>
+          <t>ROSA MARINA</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>21/02/2016</t>
+          <t>27/06/1969</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>24/08/2016</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13523,35 +13523,35 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>19870451</t>
+          <t>42350389</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ROSA MARINA</t>
+          <t>LUIS CUVIAR</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>27/06/1969</t>
+          <t>06/04/1983</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>29/11/2012</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13586,7 +13586,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>42350389</t>
+          <t>60501512</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13596,12 +13596,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LUIS CUVIAR</t>
+          <t>KENYI ANDY</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13610,21 +13610,21 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>06/04/1983</t>
+          <t>27/09/2005</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>29/11/2012</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13649,7 +13649,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>60501512</t>
+          <t>62232531</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13664,20 +13664,20 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>KENYI ANDY</t>
+          <t>SARELY</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>27/09/2005</t>
+          <t>19/11/2008</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13712,7 +13712,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>62232531</t>
+          <t>19967640</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13722,35 +13722,35 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>SARELY</t>
+          <t>DIONISIO HUGO</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>19/11/2008</t>
+          <t>17/11/1959</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13775,7 +13775,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>19967640</t>
+          <t>20406209</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DIONISIO HUGO</t>
+          <t>SILVINO AURELIO</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13799,21 +13799,21 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>17/11/1959</t>
+          <t>15/10/1968</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>15/11/2019</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13838,7 +13838,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>20406209</t>
+          <t>91589995</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13848,30 +13848,30 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>SOTELO</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>SILVINO AURELIO</t>
+          <t>EYMI ETHEL</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>15/10/1968</t>
+          <t>13/11/2019</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>15/11/2019</t>
+          <t>13/11/2024</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13901,22 +13901,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>91589995</t>
+          <t>20410598</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>YUPANQUI</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SOTELO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>EYMI ETHEL</t>
+          <t>JUANA ESPERANZA</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13925,16 +13925,16 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>13/11/2019</t>
+          <t>30/12/1954</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>13/11/2024</t>
+          <t>29/08/2014</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13964,7 +13964,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>20410598</t>
+          <t>19846445</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>JUANA ESPERANZA</t>
+          <t>LUCILA</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13988,11 +13988,11 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>30/12/1954</t>
+          <t>12/12/1958</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>29/08/2014</t>
+          <t>06/04/2015</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14027,7 +14027,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>19846445</t>
+          <t>44438775</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LUCILA</t>
+          <t>EUDOVIA FLORINDA</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14051,21 +14051,21 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>12/12/1958</t>
+          <t>15/10/1976</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>11/11/2013</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14084,69 +14084,6 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>120605</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>44438775</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>YUPANQUI</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>PARIACHI</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>EUDOVIA FLORINDA</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F218" t="n">
-        <v>50</v>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>15/10/1976</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>11/11/2013</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>PAMPA HERMOSA</t>
-        </is>
-      </c>
-      <c r="M218" t="n">
         <v>120605</v>
       </c>
     </row>

--- a/exports/6876_toldopampa.xlsx
+++ b/exports/6876_toldopampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M217"/>
+  <dimension ref="A1:M219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11066,35 +11066,35 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>47491387</t>
+          <t>20437301</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ADRIAN ZOSIMO</t>
+          <t>ELIZABETH LUZMILA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>14/10/1991</t>
+          <t>15/06/1974</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11129,22 +11129,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>74281902</t>
+          <t>47491387</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MARTEL</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>YOSVI FRANK</t>
+          <t>ADRIAN ZOSIMO</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11153,21 +11153,21 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>09/05/2000</t>
+          <t>14/10/1991</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>15/08/2019</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11192,7 +11192,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>60365239</t>
+          <t>74281902</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11207,20 +11207,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>MAILEN MELINDA</t>
+          <t>YOSVI FRANK</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>21/04/2008</t>
+          <t>09/05/2000</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>15/08/2019</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11255,7 +11255,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>93776780</t>
+          <t>60365239</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>YAÑAC</t>
+          <t>MARTEL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>BRIANA LIA</t>
+          <t>MAILEN MELINDA</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11279,21 +11279,21 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>29/03/2024</t>
+          <t>21/04/2008</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11318,7 +11318,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>41858657</t>
+          <t>93776780</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11328,35 +11328,35 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>YAÑAC</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>RUBEN GEREMIAS</t>
+          <t>BRIANA LIA</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>19/12/1979</t>
+          <t>29/03/2024</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>28/05/2018</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11381,35 +11381,35 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>46721950</t>
+          <t>41858657</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DOMINICA EUFRACIA</t>
+          <t>RUBEN GEREMIAS</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>01/02/1981</t>
+          <t>19/12/1979</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>16/04/2018</t>
+          <t>28/05/2018</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11444,22 +11444,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>47813535</t>
+          <t>46721950</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BORQUES</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>KARINA SUSANA</t>
+          <t>DOMINICA EUFRACIA</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11468,11 +11468,11 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>02/12/1991</t>
+          <t>01/02/1981</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>19/11/2013</t>
+          <t>16/04/2018</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11507,7 +11507,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>21002984</t>
+          <t>47813535</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11517,35 +11517,35 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>HUAMANYAURI</t>
+          <t>BORQUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NICANOR</t>
+          <t>KARINA SUSANA</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>12/01/1964</t>
+          <t>02/12/1991</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>29/11/2012</t>
+          <t>19/11/2013</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11570,7 +11570,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>62976765</t>
+          <t>21002984</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>HUAMANYAURI</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DILBER ERIK</t>
+          <t>NICANOR</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11594,21 +11594,21 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>14/04/2010</t>
+          <t>12/01/1964</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>04/01/2013</t>
+          <t>29/11/2012</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11633,7 +11633,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>62976766</t>
+          <t>62976765</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11648,20 +11648,20 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ANAYHELY ISABEL</t>
+          <t>DILBER ERIK</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>25/04/2012</t>
+          <t>14/04/2010</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11696,7 +11696,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>90592821</t>
+          <t>62976766</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11711,30 +11711,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ALEXIS CAVANI</t>
+          <t>ANAYHELY ISABEL</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>31/12/2017</t>
+          <t>25/04/2012</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>04/01/2023</t>
+          <t>04/01/2013</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11759,45 +11759,45 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>19846430</t>
+          <t>90592821</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DE BORQUEZ</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CLAUDIA</t>
+          <t>ALEXIS CAVANI</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>19/12/1949</t>
+          <t>31/12/2017</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>04/01/2023</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11822,7 +11822,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>20416934</t>
+          <t>19846430</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11832,30 +11832,30 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>DE BORQUEZ</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>CLAUDIA</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>23/02/1969</t>
+          <t>19/12/1949</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11885,7 +11885,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>75551009</t>
+          <t>20416934</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11895,35 +11895,35 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>YULISSA CYNTIA</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>15/05/1999</t>
+          <t>23/02/1969</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>23/05/2018</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11948,7 +11948,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>72574876</t>
+          <t>75551009</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11958,30 +11958,30 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>FRANKLIN JHON</t>
+          <t>YULISSA CYNTIA</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>14/11/1994</t>
+          <t>15/05/1999</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/05/2018</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -12011,45 +12011,45 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>91586076</t>
+          <t>72574876</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ZOE JULIET</t>
+          <t>FRANKLIN JHON</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>10/11/2019</t>
+          <t>14/11/1994</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>10/11/2024</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12074,45 +12074,45 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>48031859</t>
+          <t>91586076</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>KEVIN</t>
+          <t>ZOE JULIET</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>28/11/1993</t>
+          <t>10/11/2019</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>10/11/2024</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -12137,35 +12137,35 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>20412147</t>
+          <t>48031859</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SEGISMUNDA</t>
+          <t>KEVIN</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>01/05/1969</t>
+          <t>28/11/1993</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>09/03/2012</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12200,35 +12200,35 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>48834000</t>
+          <t>20412147</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BORQUEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>YECSON CARLOS</t>
+          <t>SEGISMUNDA</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>29/05/1996</t>
+          <t>01/05/1969</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>09/03/2012</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12263,35 +12263,35 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>41392203</t>
+          <t>48834000</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>BORQUEZ</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>EVELYN KARINA</t>
+          <t>YECSON CARLOS</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>04/08/1982</t>
+          <t>29/05/1996</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>15/07/2016</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12326,22 +12326,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>20985669</t>
+          <t>41392203</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ANDAMAYO</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>YOLANDA</t>
+          <t>EVELYN KARINA</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12350,16 +12350,16 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>14/02/1965</t>
+          <t>04/08/1982</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>19/08/2016</t>
+          <t>15/07/2016</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12389,7 +12389,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>61670543</t>
+          <t>20985669</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12399,12 +12399,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>AVELLANEDA</t>
+          <t>ANDAMAYO</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ANEL VICTORIA</t>
+          <t>YOLANDA</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12413,16 +12413,16 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>24/05/2009</t>
+          <t>14/02/1965</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>20/01/2012</t>
+          <t>19/08/2016</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12452,7 +12452,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>91603665</t>
+          <t>61670543</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12462,30 +12462,30 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>AVELLANEDA</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>ANEL VICTORIA</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>20/11/2019</t>
+          <t>24/05/2009</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>20/11/2024</t>
+          <t>20/01/2012</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12515,7 +12515,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>94494964</t>
+          <t>91603665</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>POCOMUCHA</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LIAM JAYDEN</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12539,11 +12539,11 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>30/12/2025</t>
+          <t>20/11/2019</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>20/11/2024</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12578,7 +12578,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>20973479</t>
+          <t>94494964</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>POCOMUCHA</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>BACELIO</t>
+          <t>LIAM JAYDEN</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12602,21 +12602,21 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>28/02/1966</t>
+          <t>30/12/2025</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>22/10/2013</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12641,45 +12641,45 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>20412276</t>
+          <t>20973479</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ROMANI</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>AIDEE OLINDA</t>
+          <t>BACELIO</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>07/09/1972</t>
+          <t>28/02/1966</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>02/05/2013</t>
+          <t>22/10/2013</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12704,22 +12704,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>91558038</t>
+          <t>20412276</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ROMANI</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LUCIANA NANCY</t>
+          <t>AIDEE OLINDA</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12728,16 +12728,16 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>24/10/2019</t>
+          <t>07/09/1972</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>02/05/2013</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12767,40 +12767,40 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>20990462</t>
+          <t>91558038</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SOTOMAYOR</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ALPINIANO</t>
+          <t>LUCIANA NANCY</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>30/06/1941</t>
+          <t>24/10/2019</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>17/12/2012</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12830,45 +12830,45 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>20996898</t>
+          <t>20990462</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SULLCARAY</t>
+          <t>SOTOMAYOR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ESCOBAR DE PEREZ</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>EUGENIA</t>
+          <t>ALPINIANO</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>03/09/1975</t>
+          <t>30/06/1941</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>17/12/2012</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12893,22 +12893,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>63260239</t>
+          <t>20996898</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>SULLCARAY</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>ESCOBAR DE PEREZ</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ANGELA DANIELA</t>
+          <t>EUGENIA</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12917,21 +12917,21 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>12/09/2011</t>
+          <t>03/09/1975</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>22/03/2012</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12956,22 +12956,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>74951390</t>
+          <t>63260239</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>USCAMAYTA</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>MEDALY MIRELLA</t>
+          <t>ANGELA DANIELA</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12980,21 +12980,21 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>23/02/2002</t>
+          <t>12/09/2011</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>22/03/2012</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13019,22 +13019,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>21011813</t>
+          <t>61744559</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TERREROS</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ESPERANZA</t>
+          <t>LESLY HEVILYN</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13043,21 +13043,21 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>08/01/1968</t>
+          <t>21/11/2002</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>05/12/2012</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13082,35 +13082,35 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>60657088</t>
+          <t>74951390</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>USCAMAYTA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>BRAYAN RIKI</t>
+          <t>MEDALY MIRELLA</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>04/12/2001</t>
+          <t>23/02/2002</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13145,35 +13145,35 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>21011828</t>
+          <t>21011813</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ENOCH ESEQUIEL</t>
+          <t>ESPERANZA</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>04/06/1971</t>
+          <t>08/01/1968</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>26/09/2012</t>
+          <t>05/12/2012</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13208,22 +13208,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>80038185</t>
+          <t>60657088</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>WILSON</t>
+          <t>BRAYAN RIKI</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13232,16 +13232,16 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>03/10/1977</t>
+          <t>04/12/2001</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>27/06/2021</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>48279651</t>
+          <t>21011828</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13281,25 +13281,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NELVA</t>
+          <t>ENOCH ESEQUIEL</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>23/05/1994</t>
+          <t>04/06/1971</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>75847039</t>
+          <t>80038185</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13344,35 +13344,35 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>SADITH</t>
+          <t>WILSON</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>01/01/2001</t>
+          <t>03/10/1977</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>27/01/2012</t>
+          <t>27/06/2021</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13397,7 +13397,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>81359236</t>
+          <t>48279651</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13407,30 +13407,30 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>CALEB JAMES</t>
+          <t>NELVA</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>21/02/2016</t>
+          <t>23/05/1994</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>24/08/2016</t>
+          <t>26/09/2012</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13460,7 +13460,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>19870451</t>
+          <t>75847039</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ROSA MARINA</t>
+          <t>SADITH</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13484,21 +13484,21 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>27/06/1969</t>
+          <t>01/01/2001</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>27/01/2012</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13523,22 +13523,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>42350389</t>
+          <t>81359236</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LUIS CUVIAR</t>
+          <t>CALEB JAMES</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13547,16 +13547,16 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>06/04/1983</t>
+          <t>21/02/2016</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>29/11/2012</t>
+          <t>24/08/2016</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13586,40 +13586,40 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>60501512</t>
+          <t>19870451</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>KENYI ANDY</t>
+          <t>ROSA MARINA</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>27/09/2005</t>
+          <t>27/06/1969</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13649,7 +13649,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>62232531</t>
+          <t>42350389</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13659,35 +13659,35 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>SARELY</t>
+          <t>LUIS CUVIAR</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>19/11/2008</t>
+          <t>06/04/1983</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>29/11/2012</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13712,7 +13712,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>19967640</t>
+          <t>60501512</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13722,12 +13722,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DIONISIO HUGO</t>
+          <t>KENYI ANDY</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13736,21 +13736,21 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>17/11/1959</t>
+          <t>27/09/2005</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13775,7 +13775,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>20406209</t>
+          <t>62232531</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13785,35 +13785,35 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>SILVINO AURELIO</t>
+          <t>SARELY</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>15/10/1968</t>
+          <t>19/11/2008</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>15/11/2019</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13838,7 +13838,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>91589995</t>
+          <t>19967640</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13848,35 +13848,35 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SOTELO</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>EYMI ETHEL</t>
+          <t>DIONISIO HUGO</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>13/11/2019</t>
+          <t>17/11/1959</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>13/11/2024</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13901,40 +13901,40 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>20410598</t>
+          <t>20406209</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>JUANA ESPERANZA</t>
+          <t>SILVINO AURELIO</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>30/12/1954</t>
+          <t>15/10/1968</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>29/08/2014</t>
+          <t>15/11/2019</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13964,22 +13964,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>19846445</t>
+          <t>91589995</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>SOTELO</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LUCILA</t>
+          <t>EYMI ETHEL</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13988,21 +13988,21 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>12/12/1958</t>
+          <t>13/11/2019</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>13/11/2024</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14027,63 +14027,189 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
+          <t>20410598</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>YUPANQUI</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>JUANA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>72</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>30/12/1954</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>5.ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>29/08/2014</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M217" t="n">
+        <v>120605</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>19846445</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>YUPANQUI</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>LUCILA</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>68</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>12/12/1958</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>5.ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>06/04/2015</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M218" t="n">
+        <v>120605</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
           <t>44438775</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>YUPANQUI</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>PARIACHI</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>EUDOVIA FLORINDA</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F217" t="n">
+      <c r="F219" t="n">
         <v>50</v>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G219" t="inlineStr">
         <is>
           <t>15/10/1976</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H219" t="inlineStr">
         <is>
           <t>4.ADULTO</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I219" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
         <is>
           <t>11/11/2013</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>PAMPA HERMOSA</t>
-        </is>
-      </c>
-      <c r="M217" t="n">
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M219" t="n">
         <v>120605</v>
       </c>
     </row>

--- a/exports/6876_toldopampa.xlsx
+++ b/exports/6876_toldopampa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M219"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>15/07/2016</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>12/03/2014</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>15/07/2016</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>06/07/2016</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>21/11/2017</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9176,40 +9176,40 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>80846850</t>
+          <t>19913016</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ARTIAGA</t>
+          <t>HUANACUNI</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>FRANZ HUGO</t>
+          <t>MARTHA</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>06/07/2013</t>
+          <t>13/01/1964</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20/02/2014</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9239,7 +9239,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>75561463</t>
+          <t>80846850</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>ARTIAGA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>FRANK ERWIN</t>
+          <t>FRANZ HUGO</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9263,21 +9263,21 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>09/05/2001</t>
+          <t>06/07/2013</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>28/06/2020</t>
+          <t>20/02/2014</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9302,7 +9302,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>20972935</t>
+          <t>75561463</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LLALLICO</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>EMILIO</t>
+          <t>FRANK ERWIN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9326,21 +9326,21 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>03/05/1938</t>
+          <t>09/05/2001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>28/06/2020</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9365,45 +9365,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>60501511</t>
+          <t>20972935</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MARTEL</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>LLALLICO</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>MERLY GEOVANA</t>
+          <t>EMILIO</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>22/08/2007</t>
+          <t>03/05/1938</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9428,7 +9428,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>20405874</t>
+          <t>60501511</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9438,35 +9438,35 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>FLORIANO</t>
+          <t>MERLY GEOVANA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>17/12/1967</t>
+          <t>22/08/2007</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>21/05/2021</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9491,7 +9491,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>20439623</t>
+          <t>20405874</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>YONI MESIAS</t>
+          <t>FLORIANO</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9515,11 +9515,11 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>05/10/1976</t>
+          <t>17/12/1967</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>27/07/2013</t>
+          <t>21/05/2021</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9554,7 +9554,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>47763747</t>
+          <t>20439623</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>WILLIAM</t>
+          <t>YONI MESIAS</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>01/04/1993</t>
+          <t>05/10/1976</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>26/09/2013</t>
+          <t>27/07/2013</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9617,35 +9617,35 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>40897087</t>
+          <t>47763747</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MARTEL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>MARLENY FLORA</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>16/11/1980</t>
+          <t>01/04/1993</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>26/09/2013</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9680,22 +9680,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>76852567</t>
+          <t>40897087</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CUADROS</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>INES MARIBEL</t>
+          <t>MARLENY FLORA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>24/05/1994</t>
+          <t>16/11/1980</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9743,7 +9743,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>44637444</t>
+          <t>76852567</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9753,25 +9753,25 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>CUADROS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ELIAS</t>
+          <t>INES MARIBEL</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>14/04/1980</t>
+          <t>24/05/1994</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9806,22 +9806,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>43056031</t>
+          <t>44637444</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ORLANDO</t>
+          <t>ELIAS</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9830,11 +9830,11 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>26/04/1982</t>
+          <t>14/04/1980</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>31/01/2020</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9869,7 +9869,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>60845229</t>
+          <t>43056031</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9879,35 +9879,35 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>JULIA ISAMAR</t>
+          <t>ORLANDO</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>26/04/1982</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9932,7 +9932,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>91308982</t>
+          <t>60845229</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SAURI KINVERLY</t>
+          <t>JULIA ISAMAR</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9956,21 +9956,21 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>04/01/2019</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>04/01/2024</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9995,7 +9995,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>92153987</t>
+          <t>91308982</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10005,30 +10005,30 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>CRISTIAN BEKER</t>
+          <t>SAURI KINVERLY</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>08/12/2007</t>
+          <t>04/01/2019</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>18/05/2021</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10058,22 +10058,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>91558326</t>
+          <t>92153987</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MOYA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>VILLALVA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>FREY ANGELO SMITH</t>
+          <t>CRISTIAN BEKER</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10082,16 +10082,16 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>23/10/2019</t>
+          <t>08/12/2007</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>23/10/2024</t>
+          <t>18/05/2021</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10121,22 +10121,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>42381881</t>
+          <t>91558326</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>MOYA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>VILLALVA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>CESAR</t>
+          <t>FREY ANGELO SMITH</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10145,16 +10145,16 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>19/02/1983</t>
+          <t>23/10/2019</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>15/07/2016</t>
+          <t>23/10/2024</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10184,7 +10184,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>49030900</t>
+          <t>42381881</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10194,30 +10194,30 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>FIBIANA</t>
+          <t>CESAR</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>25/05/1944</t>
+          <t>19/02/1983</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>29/01/2020</t>
+          <t>15/07/2016</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10247,45 +10247,45 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>94502900</t>
+          <t>49030900</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AVELLANEDA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>YAMPOL KALETH</t>
+          <t>FIBIANA</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>25/05/1944</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>29/01/2020</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10310,7 +10310,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>48869165</t>
+          <t>94502900</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10320,35 +10320,35 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>AVELLANEDA</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ELISA</t>
+          <t>YAMPOL KALETH</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>04/01/1998</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>15/10/2018</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10373,7 +10373,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>45441610</t>
+          <t>48869165</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10383,30 +10383,30 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ILDEFONSO</t>
+          <t>ELISA</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>23/01/1987</t>
+          <t>04/01/1998</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>15/10/2018</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10436,22 +10436,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>20438345</t>
+          <t>45441610</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>JULIO</t>
+          <t>ILDEFONSO</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10460,16 +10460,16 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>01/07/1957</t>
+          <t>23/01/1987</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10499,45 +10499,45 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>40567779</t>
+          <t>20438345</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PARIONA DE MORALES</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>INES EULALIA</t>
+          <t>JULIO</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>10/04/1980</t>
+          <t>01/07/1957</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10562,22 +10562,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>75789175</t>
+          <t>40567779</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CANCHUMUNIA</t>
+          <t>PARIONA DE MORALES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NAYELI NEYRA</t>
+          <t>INES EULALIA</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10586,21 +10586,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>10/04/1980</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10625,7 +10625,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>45115006</t>
+          <t>75789175</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CANCHUMUNIA</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ANA YSABEL</t>
+          <t>NAYELI NEYRA</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10649,21 +10649,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>25/12/1987</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>60365230</t>
+          <t>45115006</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>HILARIO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>YANY ANGELA</t>
+          <t>ANA YSABEL</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10712,21 +10712,21 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>09/03/2008</t>
+          <t>25/12/1987</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10751,7 +10751,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>90666210</t>
+          <t>60365230</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>GAEL FELIPE</t>
+          <t>YANY ANGELA</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>13/09/2017</t>
+          <t>09/03/2008</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>13/09/2022</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10814,7 +10814,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>19846456</t>
+          <t>90666210</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HUAYCANE</t>
+          <t>HILARIO</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>FELIX NARCISO</t>
+          <t>GAEL FELIPE</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10838,21 +10838,21 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>25/02/1956</t>
+          <t>13/09/2017</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10877,7 +10877,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>46254489</t>
+          <t>19846456</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10887,35 +10887,35 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>HUAYCANE</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>GLORIA OLGA</t>
+          <t>FELIX NARCISO</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>26/12/1986</t>
+          <t>25/02/1956</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>05/09/2018</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10940,7 +10940,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>48583203</t>
+          <t>46254489</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VICTORIA ZORAYDA</t>
+          <t>GLORIA OLGA</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10964,11 +10964,11 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>19/06/1994</t>
+          <t>26/12/1986</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>11/08/2014</t>
+          <t>05/09/2018</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11003,7 +11003,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>44279322</t>
+          <t>48583203</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>MARLENE</t>
+          <t>VICTORIA ZORAYDA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11027,11 +11027,11 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>25/05/1987</t>
+          <t>19/06/1994</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>07/08/2011</t>
+          <t>11/08/2014</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11066,22 +11066,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>20437301</t>
+          <t>44279322</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>YUPANQUI</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ELIZABETH LUZMILA</t>
+          <t>MARLENE</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11090,11 +11090,11 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>15/06/1974</t>
+          <t>25/05/1987</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>07/08/2011</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11129,35 +11129,35 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>47491387</t>
+          <t>20437301</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ADRIAN ZOSIMO</t>
+          <t>ELIZABETH LUZMILA</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>14/10/1991</t>
+          <t>15/06/1974</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11192,22 +11192,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>74281902</t>
+          <t>47491387</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MARTEL</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>YOSVI FRANK</t>
+          <t>ADRIAN ZOSIMO</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11216,21 +11216,21 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>09/05/2000</t>
+          <t>14/10/1991</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>15/08/2019</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13862,7 +13862,7 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -14027,40 +14027,40 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>20410598</t>
+          <t>78343147</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>YAURI</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>JUANA ESPERANZA</t>
+          <t>THIAGO BENJAMIN</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>30/12/1954</t>
+          <t>11/11/2013</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>29/08/2014</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14090,7 +14090,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>19846445</t>
+          <t>20410598</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LUCILA</t>
+          <t>JUANA ESPERANZA</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -14114,11 +14114,11 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>12/12/1958</t>
+          <t>30/12/1954</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>29/08/2014</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14153,63 +14153,126 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
+          <t>19846445</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>YUPANQUI</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>LUCILA</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>67</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>12/12/1958</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>5.ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>06/04/2015</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M219" t="n">
+        <v>120605</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
           <t>44438775</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>YUPANQUI</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>PARIACHI</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>EUDOVIA FLORINDA</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F219" t="n">
+      <c r="F220" t="n">
         <v>50</v>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G220" t="inlineStr">
         <is>
           <t>15/10/1976</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H220" t="inlineStr">
         <is>
           <t>4.ADULTO</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I220" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
         <is>
           <t>11/11/2013</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>PAMPA HERMOSA</t>
-        </is>
-      </c>
-      <c r="M219" t="n">
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M220" t="n">
         <v>120605</v>
       </c>
     </row>
